--- a/summary_latest_v2.xlsx
+++ b/summary_latest_v2.xlsx
@@ -881,10 +881,10 @@
         <v>69</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>6.2</v>
@@ -968,10 +968,10 @@
         <v>82</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>90.3</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>90.3</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4.3</v>
@@ -1142,10 +1142,10 @@
         <v>82.2</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>72.2</v>
+        <v>72.22</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>70.37</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>20.6</v>
@@ -1490,10 +1490,10 @@
         <v>68.3</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>73.7</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>73.7</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>8.5</v>
@@ -1577,10 +1577,10 @@
         <v>67.09999999999999</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>7.9</v>
@@ -1664,10 +1664,10 @@
         <v>65.7</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>0</v>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.3% alvo @34.94 (WR 75% / alvo 73%) * Stop @31.54 (-6.8%) * Cancelar se &lt; MA50/S1 @32.28</t>
+          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.9% alvo @34.36 (WR 75% / alvo 73%) * Stop @32.42 (-2.0%) * Cancelar se &lt; MA50/S1 @32.28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1718,22 +1718,22 @@
         <v>33.25</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>33.8438</v>
+        <v>33.0838</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>33.915</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>31.5447</v>
+        <v>32.4221</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>34.9438</v>
+        <v>34.3611</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>32.2805</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>33.81</v>
@@ -1751,10 +1751,10 @@
         <v>80.5</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>73.13</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>21.6</v>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ORDEM LIMITE @13.19 * S2 Alta momentum * +4.1% alvo @13.73 (WR 67% / alvo 66%) * Stop @12.75 (-3.3%) * Cancelar se &lt; MA50/S1 @11.81</t>
+          <t>ORDEM LIMITE @13.11 * S2 Alta momentum * +3.0% alvo @13.50 (WR 67% / alvo 66%) * Stop @12.84 (-2.0%) * Cancelar se &lt; MA50/S1 @11.81</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1805,22 +1805,22 @@
         <v>13.31</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>13.1897</v>
+        <v>13.1059</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.5762</v>
+        <v>13.364</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>12.7491</v>
+        <v>12.8438</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>13.7266</v>
+        <v>13.499</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>11.8072</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>13.2767</v>
@@ -1838,10 +1838,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>67.2</v>
+        <v>67.19</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>65.62</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>11.6</v>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AGUARDAR ROMPER PIVOT @29.38 * S2 Alta momentum * +3.4% alvo @30.42 (WR 69% / alvo 69%) * Stop @27.63 (-6.1%) * Cancelar se &lt; MA50/S1 @27.02</t>
+          <t>AGUARDAR ROMPER PIVOT @29.38 * S2 Alta momentum * +4.0% alvo @30.00 (WR 69% / alvo 69%) * Stop @28.16 (-2.3%) * Cancelar se &lt; MA50/S1 @27.02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1892,22 +1892,22 @@
         <v>28.98</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>29.4094</v>
+        <v>28.8351</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>29.5596</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>27.6263</v>
+        <v>28.1585</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>30.4219</v>
+        <v>29.9999</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>27.0214</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>29.38</v>
@@ -1925,10 +1925,10 @@
         <v>79.5</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>16.7</v>
@@ -2447,10 +2447,10 @@
         <v>62.2</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U21" s="5" t="n">
         <v>5.2</v>
@@ -2534,10 +2534,10 @@
         <v>63.9</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U22" s="5" t="n">
         <v>5.2</v>
@@ -2621,10 +2621,10 @@
         <v>63.7</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>81.8</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>72.7</v>
+        <v>72.73</v>
       </c>
       <c r="U23" s="5" t="n">
         <v>3.7</v>
@@ -2795,10 +2795,10 @@
         <v>62.5</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>68.8</v>
+        <v>68.75</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>56.2</v>
+        <v>56.25</v>
       </c>
       <c r="U25" s="5" t="n">
         <v>5.5</v>
@@ -3056,10 +3056,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>63.8</v>
+        <v>63.77</v>
       </c>
       <c r="U28" s="5" t="n">
         <v>14.6</v>
@@ -3143,10 +3143,10 @@
         <v>60.3</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="U29" s="5" t="n">
         <v>11.3</v>
@@ -3230,10 +3230,10 @@
         <v>61.6</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="U30" s="5" t="n">
         <v>4.7</v>
@@ -3317,10 +3317,10 @@
         <v>61.1</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U31" s="5" t="n">
         <v>7.3</v>
@@ -3404,10 +3404,10 @@
         <v>60.9</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U32" s="5" t="n">
         <v>3.7</v>
@@ -3491,10 +3491,10 @@
         <v>61.9</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U33" s="5" t="n">
         <v>4.7</v>
@@ -3578,10 +3578,10 @@
         <v>62.5</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U34" s="5" t="n">
         <v>6.1</v>
@@ -3752,10 +3752,10 @@
         <v>58.8</v>
       </c>
       <c r="S36" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U36" s="5" t="n">
         <v>4.4</v>
@@ -3926,10 +3926,10 @@
         <v>52.5</v>
       </c>
       <c r="S38" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="U38" s="5" t="n">
         <v>14.4</v>
@@ -4100,10 +4100,10 @@
         <v>56.6</v>
       </c>
       <c r="S40" s="5" t="n">
-        <v>61.5</v>
+        <v>61.54</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>53.8</v>
+        <v>53.85</v>
       </c>
       <c r="U40" s="5" t="n">
         <v>16</v>
@@ -4274,10 +4274,10 @@
         <v>58.2</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U42" s="5" t="n">
         <v>5.2</v>
@@ -4361,10 +4361,10 @@
         <v>54</v>
       </c>
       <c r="S43" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U43" s="5" t="n">
         <v>6.6</v>
@@ -4448,10 +4448,10 @@
         <v>54.9</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U44" s="5" t="n">
         <v>3.2</v>
@@ -4535,10 +4535,10 @@
         <v>54.1</v>
       </c>
       <c r="S45" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="U45" s="5" t="n">
         <v>14.2</v>
@@ -4970,10 +4970,10 @@
         <v>51.5</v>
       </c>
       <c r="S50" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U50" s="5" t="n">
         <v>3.7</v>
@@ -7667,10 +7667,10 @@
         <v>36.4</v>
       </c>
       <c r="S81" s="5" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="U81" s="5" t="n">
         <v>10.5</v>
@@ -9059,7 +9059,7 @@
         <v>44.2</v>
       </c>
       <c r="S97" s="5" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T97" s="5" t="n">
         <v>0</v>
@@ -9407,10 +9407,10 @@
         <v>49.8</v>
       </c>
       <c r="S101" s="5" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="U101" s="5" t="n">
         <v>5.2</v>
@@ -9929,7 +9929,7 @@
         <v>41.3</v>
       </c>
       <c r="S107" s="5" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T107" s="5" t="n">
         <v>0</v>
@@ -10277,10 +10277,10 @@
         <v>48.7</v>
       </c>
       <c r="S111" s="5" t="n">
-        <v>72.7</v>
+        <v>72.73</v>
       </c>
       <c r="T111" s="5" t="n">
-        <v>45.5</v>
+        <v>45.45</v>
       </c>
       <c r="U111" s="5" t="n">
         <v>9.6</v>
@@ -10364,10 +10364,10 @@
         <v>71.2</v>
       </c>
       <c r="S112" s="5" t="n">
-        <v>73.8</v>
+        <v>73.77</v>
       </c>
       <c r="T112" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="U112" s="5" t="n">
         <v>9.5</v>
@@ -74687,10 +74687,10 @@
         <v>69</v>
       </c>
       <c r="S3" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T3" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="U3" t="n">
         <v>6.2</v>
@@ -74792,10 +74792,10 @@
         <v>82</v>
       </c>
       <c r="S4" t="n">
-        <v>90.3</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>90.3</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="U4" t="n">
         <v>4.3</v>
@@ -75002,10 +75002,10 @@
         <v>82.2</v>
       </c>
       <c r="S6" t="n">
-        <v>72.2</v>
+        <v>72.22</v>
       </c>
       <c r="T6" t="n">
-        <v>70.40000000000001</v>
+        <v>70.37</v>
       </c>
       <c r="U6" t="n">
         <v>20.6</v>
@@ -75422,10 +75422,10 @@
         <v>68.3</v>
       </c>
       <c r="S10" t="n">
-        <v>73.7</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>73.7</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="U10" t="n">
         <v>8.5</v>
@@ -75527,10 +75527,10 @@
         <v>67.09999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T11" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="U11" t="n">
         <v>7.9</v>
@@ -75632,10 +75632,10 @@
         <v>65.7</v>
       </c>
       <c r="S12" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T12" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -75682,12 +75682,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.3% alvo @34.94 (WR 75% / alvo 73%) * Stop @31.54 (-6.8%) * Cancelar se &lt; MA50/S1 @32.28</t>
+          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.9% alvo @34.36 (WR 75% / alvo 73%) * Stop @32.42 (-2.0%) * Cancelar se &lt; MA50/S1 @32.28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -75704,22 +75704,22 @@
         <v>33.25</v>
       </c>
       <c r="H13" t="n">
-        <v>33.8438</v>
+        <v>33.0838</v>
       </c>
       <c r="I13" t="n">
         <v>33.915</v>
       </c>
       <c r="J13" t="n">
-        <v>31.5447</v>
+        <v>32.4221</v>
       </c>
       <c r="K13" t="n">
-        <v>34.9438</v>
+        <v>34.3611</v>
       </c>
       <c r="L13" t="n">
         <v>32.2805</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="N13" t="n">
         <v>33.81</v>
@@ -75737,10 +75737,10 @@
         <v>80.5</v>
       </c>
       <c r="S13" t="n">
-        <v>75.40000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="T13" t="n">
-        <v>73.09999999999999</v>
+        <v>73.13</v>
       </c>
       <c r="U13" t="n">
         <v>21.6</v>
@@ -75787,12 +75787,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORDEM LIMITE @13.19 * S2 Alta momentum * +4.1% alvo @13.73 (WR 67% / alvo 66%) * Stop @12.75 (-3.3%) * Cancelar se &lt; MA50/S1 @11.81</t>
+          <t>ORDEM LIMITE @13.11 * S2 Alta momentum * +3.0% alvo @13.50 (WR 67% / alvo 66%) * Stop @12.84 (-2.0%) * Cancelar se &lt; MA50/S1 @11.81</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -75809,22 +75809,22 @@
         <v>13.31</v>
       </c>
       <c r="H14" t="n">
-        <v>13.1897</v>
+        <v>13.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>13.5762</v>
+        <v>13.364</v>
       </c>
       <c r="J14" t="n">
-        <v>12.7491</v>
+        <v>12.8438</v>
       </c>
       <c r="K14" t="n">
-        <v>13.7266</v>
+        <v>13.499</v>
       </c>
       <c r="L14" t="n">
         <v>11.8072</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="N14" t="n">
         <v>13.2767</v>
@@ -75842,10 +75842,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>67.2</v>
+        <v>67.19</v>
       </c>
       <c r="T14" t="n">
-        <v>65.59999999999999</v>
+        <v>65.62</v>
       </c>
       <c r="U14" t="n">
         <v>11.6</v>
@@ -75892,12 +75892,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AGUARDAR ROMPER PIVOT @29.38 * S2 Alta momentum * +3.4% alvo @30.42 (WR 69% / alvo 69%) * Stop @27.63 (-6.1%) * Cancelar se &lt; MA50/S1 @27.02</t>
+          <t>AGUARDAR ROMPER PIVOT @29.38 * S2 Alta momentum * +4.0% alvo @30.00 (WR 69% / alvo 69%) * Stop @28.16 (-2.3%) * Cancelar se &lt; MA50/S1 @27.02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -75914,22 +75914,22 @@
         <v>28.98</v>
       </c>
       <c r="H15" t="n">
-        <v>29.4094</v>
+        <v>28.8351</v>
       </c>
       <c r="I15" t="n">
         <v>29.5596</v>
       </c>
       <c r="J15" t="n">
-        <v>27.6263</v>
+        <v>28.1585</v>
       </c>
       <c r="K15" t="n">
-        <v>30.4219</v>
+        <v>29.9999</v>
       </c>
       <c r="L15" t="n">
         <v>27.0214</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="N15" t="n">
         <v>29.38</v>
@@ -75947,10 +75947,10 @@
         <v>79.5</v>
       </c>
       <c r="S15" t="n">
-        <v>68.59999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>68.59999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>16.7</v>
@@ -76577,10 +76577,10 @@
         <v>62.2</v>
       </c>
       <c r="S21" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T21" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U21" t="n">
         <v>5.2</v>
@@ -76682,10 +76682,10 @@
         <v>63.9</v>
       </c>
       <c r="S22" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U22" t="n">
         <v>5.2</v>
@@ -76787,10 +76787,10 @@
         <v>63.7</v>
       </c>
       <c r="S23" t="n">
-        <v>81.8</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>72.7</v>
+        <v>72.73</v>
       </c>
       <c r="U23" t="n">
         <v>3.7</v>
@@ -76997,10 +76997,10 @@
         <v>62.5</v>
       </c>
       <c r="S25" t="n">
-        <v>68.8</v>
+        <v>68.75</v>
       </c>
       <c r="T25" t="n">
-        <v>56.2</v>
+        <v>56.25</v>
       </c>
       <c r="U25" t="n">
         <v>5.5</v>
@@ -77312,10 +77312,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T28" t="n">
-        <v>63.8</v>
+        <v>63.77</v>
       </c>
       <c r="U28" t="n">
         <v>14.6</v>
@@ -77417,10 +77417,10 @@
         <v>60.3</v>
       </c>
       <c r="S29" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T29" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="U29" t="n">
         <v>11.3</v>
@@ -77522,10 +77522,10 @@
         <v>61.6</v>
       </c>
       <c r="S30" t="n">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="T30" t="n">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="U30" t="n">
         <v>4.7</v>
@@ -77627,10 +77627,10 @@
         <v>61.1</v>
       </c>
       <c r="S31" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T31" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U31" t="n">
         <v>7.3</v>
@@ -77732,10 +77732,10 @@
         <v>60.9</v>
       </c>
       <c r="S32" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T32" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U32" t="n">
         <v>3.7</v>
@@ -77837,10 +77837,10 @@
         <v>61.9</v>
       </c>
       <c r="S33" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="T33" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U33" t="n">
         <v>4.7</v>
@@ -77942,10 +77942,10 @@
         <v>62.5</v>
       </c>
       <c r="S34" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="T34" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U34" t="n">
         <v>6.1</v>
@@ -78152,10 +78152,10 @@
         <v>58.8</v>
       </c>
       <c r="S36" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T36" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U36" t="n">
         <v>4.4</v>
@@ -78362,10 +78362,10 @@
         <v>52.5</v>
       </c>
       <c r="S38" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T38" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="U38" t="n">
         <v>14.4</v>
@@ -78572,10 +78572,10 @@
         <v>56.6</v>
       </c>
       <c r="S40" t="n">
-        <v>61.5</v>
+        <v>61.54</v>
       </c>
       <c r="T40" t="n">
-        <v>53.8</v>
+        <v>53.85</v>
       </c>
       <c r="U40" t="n">
         <v>16</v>
@@ -78782,10 +78782,10 @@
         <v>58.2</v>
       </c>
       <c r="S42" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T42" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U42" t="n">
         <v>5.2</v>
@@ -78887,10 +78887,10 @@
         <v>54</v>
       </c>
       <c r="S43" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T43" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U43" t="n">
         <v>6.6</v>
@@ -78992,10 +78992,10 @@
         <v>54.9</v>
       </c>
       <c r="S44" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T44" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="U44" t="n">
         <v>3.2</v>
@@ -79097,10 +79097,10 @@
         <v>54.1</v>
       </c>
       <c r="S45" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T45" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="U45" t="n">
         <v>14.2</v>
@@ -79622,10 +79622,10 @@
         <v>51.5</v>
       </c>
       <c r="S50" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="T50" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="U50" t="n">
         <v>3.7</v>
@@ -82877,10 +82877,10 @@
         <v>36.4</v>
       </c>
       <c r="S81" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="T81" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="U81" t="n">
         <v>10.5</v>
@@ -84557,7 +84557,7 @@
         <v>44.2</v>
       </c>
       <c r="S97" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
@@ -84977,10 +84977,10 @@
         <v>49.8</v>
       </c>
       <c r="S101" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="T101" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="U101" t="n">
         <v>5.2</v>
@@ -85607,7 +85607,7 @@
         <v>41.3</v>
       </c>
       <c r="S107" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="T107" t="n">
         <v>0</v>
@@ -86027,10 +86027,10 @@
         <v>48.7</v>
       </c>
       <c r="S111" t="n">
-        <v>72.7</v>
+        <v>72.73</v>
       </c>
       <c r="T111" t="n">
-        <v>45.5</v>
+        <v>45.45</v>
       </c>
       <c r="U111" t="n">
         <v>9.6</v>
@@ -86132,10 +86132,10 @@
         <v>71.2</v>
       </c>
       <c r="S112" t="n">
-        <v>73.8</v>
+        <v>73.77</v>
       </c>
       <c r="T112" t="n">
-        <v>68.90000000000001</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="U112" t="n">
         <v>9.5</v>

--- a/summary_latest_v2.xlsx
+++ b/summary_latest_v2.xlsx
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.9% alvo @34.36 (WR 75% / alvo 73%) * Stop @32.42 (-2.0%) * Cancelar se &lt; MA50/S1 @32.28</t>
+          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.9% alvo @34.36 (WR 75% / alvo 73%) * Stop @32.47 (-1.9%) * Cancelar se &lt; MA50/S1 @32.28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
         <v>33.915</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>32.4221</v>
+        <v>32.4668</v>
       </c>
       <c r="K13" s="8" t="n">
         <v>34.3611</v>
@@ -1733,7 +1733,7 @@
         <v>32.2805</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>33.81</v>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ORDEM LIMITE @13.11 * S2 Alta momentum * +3.0% alvo @13.50 (WR 67% / alvo 66%) * Stop @12.84 (-2.0%) * Cancelar se &lt; MA50/S1 @11.81</t>
+          <t>ORDEM LIMITE @13.11 * S2 Alta momentum * +2.2% alvo @13.40 (WR 67% / alvo 66%) * Stop @12.75 (-2.7%) * Cancelar se &lt; MA50/S1 @11.81</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1808,19 +1808,19 @@
         <v>13.1059</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.364</v>
+        <v>13.2626</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>12.8438</v>
+        <v>12.7491</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>13.499</v>
+        <v>13.3966</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>11.8072</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>13.2767</v>
@@ -75682,7 +75682,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.9% alvo @34.36 (WR 75% / alvo 73%) * Stop @32.42 (-2.0%) * Cancelar se &lt; MA50/S1 @32.28</t>
+          <t>AGUARDAR ROMPER PIVOT @33.81 * S2 Alta momentum * +3.9% alvo @34.36 (WR 75% / alvo 73%) * Stop @32.47 (-1.9%) * Cancelar se &lt; MA50/S1 @32.28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -75710,7 +75710,7 @@
         <v>33.915</v>
       </c>
       <c r="J13" t="n">
-        <v>32.4221</v>
+        <v>32.4668</v>
       </c>
       <c r="K13" t="n">
         <v>34.3611</v>
@@ -75719,7 +75719,7 @@
         <v>32.2805</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="N13" t="n">
         <v>33.81</v>
@@ -75787,12 +75787,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORDEM LIMITE @13.11 * S2 Alta momentum * +3.0% alvo @13.50 (WR 67% / alvo 66%) * Stop @12.84 (-2.0%) * Cancelar se &lt; MA50/S1 @11.81</t>
+          <t>ORDEM LIMITE @13.11 * S2 Alta momentum * +2.2% alvo @13.40 (WR 67% / alvo 66%) * Stop @12.75 (-2.7%) * Cancelar se &lt; MA50/S1 @11.81</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -75812,19 +75812,19 @@
         <v>13.1059</v>
       </c>
       <c r="I14" t="n">
-        <v>13.364</v>
+        <v>13.2626</v>
       </c>
       <c r="J14" t="n">
-        <v>12.8438</v>
+        <v>12.7491</v>
       </c>
       <c r="K14" t="n">
-        <v>13.499</v>
+        <v>13.3966</v>
       </c>
       <c r="L14" t="n">
         <v>11.8072</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="n">
         <v>13.2767</v>
